--- a/backend/data/Sample_PO_File.xlsx
+++ b/backend/data/Sample_PO_File.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,178 +436,543 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>PO Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Line #</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Unit Price (USD)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Total (USD)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Validation Result</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PO001</t>
+          <t>PO-2024-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ITEM001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Vendor A</t>
-        </is>
+          <t>BuildRight Supplies Ltd</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1200</v>
+          <t>ITM-1001</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Heavy Duty Steel Bolt M12</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>500</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Each</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J2" t="n">
+        <v>425</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>✅ PASS — Active code</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PO001</t>
+          <t>PO-2024-001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ITEM999</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Vendor A</t>
-        </is>
+          <t>BuildRight Supplies Ltd</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>15</v>
+          <t>ITM-1004</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Safety Gloves (L)</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pair</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>144</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>✅ PASS — Active code</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PO002</t>
+          <t>PO-2024-001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ITEM002</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Vendor B</t>
-        </is>
+          <t>BuildRight Supplies Ltd</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>300</v>
+          <t>ITM-1011</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fire Extinguisher 2kg</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>42</v>
+      </c>
+      <c r="J4" t="n">
+        <v>210</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>✅ PASS — Active code</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PO002</t>
+          <t>PO-2024-002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ITEM003</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Vendor C</t>
-        </is>
+          <t>ElectroPro Distributors</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>25</v>
+          <t>OLD-CABLE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2.5mm Cable 100m</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>95</v>
+      </c>
+      <c r="J5" t="n">
+        <v>950</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>⚠️ MAP — OLD-CABLE → ITM-1006</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PO003</t>
+          <t>PO-2024-002</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ITEM999</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Vendor D</t>
-        </is>
+          <t>ElectroPro Distributors</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+          <t>OLD-FLOOD</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>500W Halogen Flood</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>55</v>
+      </c>
+      <c r="J6" t="n">
+        <v>220</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>⚠️ MAP — OLD-FLOOD → ITM-1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PO-2024-002</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ElectroPro Distributors</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ITM-1013</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Cable Ties 300mm (100pk)</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>63</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>✅ PASS — Active code</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PO-2024-003</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GeneralTrade Co.</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ITM-1008</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Concrete Mix 25kg</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bag</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="J8" t="n">
+        <v>675</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>✅ PASS — Active code</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PO-2024-003</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GeneralTrade Co.</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ITM-9999</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Unknown Widget XR7</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Each</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>15</v>
+      </c>
+      <c r="J9" t="n">
+        <v>750</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>❌ BLOCK — Code not in item master</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PO-2024-003</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GeneralTrade Co.</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ASBESTOS-01</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Asbestos Sheet (legacy)</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>❌ BLOCK — Code not in master / deactivated</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PO-2024-003</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-12-05</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GeneralTrade Co.</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ITM-1015</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Silicone Sealant 300ml</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Tube</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>174</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>✅ PASS — Active code</t>
+        </is>
       </c>
     </row>
   </sheetData>
